--- a/Output Data Tables/AFAT Outputs/Employee Tables/2022/Employees_by_Airline_2022.xlsx
+++ b/Output Data Tables/AFAT Outputs/Employee Tables/2022/Employees_by_Airline_2022.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="46" uniqueCount="46">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -184,7 +196,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -212,55 +224,55 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2">
@@ -1556,54 +1568,278 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>990</v>
+      </c>
+      <c r="C25" s="0">
+        <v>38624</v>
+      </c>
+      <c r="D25" s="0">
+        <v>0</v>
+      </c>
+      <c r="E25" s="0">
+        <v>63344</v>
+      </c>
+      <c r="F25" s="0">
+        <v>30694</v>
+      </c>
+      <c r="G25" s="0">
+        <v>0</v>
+      </c>
+      <c r="H25" s="0">
+        <v>15482</v>
+      </c>
+      <c r="I25" s="0">
+        <v>2490</v>
+      </c>
+      <c r="J25" s="0">
+        <v>59382</v>
+      </c>
+      <c r="K25" s="0">
+        <v>19557</v>
+      </c>
+      <c r="L25" s="0">
+        <v>3730</v>
+      </c>
+      <c r="M25" s="0">
+        <v>15271</v>
+      </c>
+      <c r="N25" s="0">
+        <v>3800</v>
+      </c>
+      <c r="O25" s="0">
+        <v>15861</v>
+      </c>
+      <c r="P25" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="0">
+        <v>269225</v>
+      </c>
+      <c r="R25" s="0">
+        <v>269225</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>2326</v>
+      </c>
+      <c r="C26" s="0">
+        <v>17322</v>
+      </c>
+      <c r="D26" s="0">
+        <v>167</v>
+      </c>
+      <c r="E26" s="0">
+        <v>30974</v>
+      </c>
+      <c r="F26" s="0">
+        <v>5313</v>
+      </c>
+      <c r="G26" s="0">
+        <v>7</v>
+      </c>
+      <c r="H26" s="0">
+        <v>5313</v>
+      </c>
+      <c r="I26" s="0">
+        <v>1374</v>
+      </c>
+      <c r="J26" s="0">
+        <v>19683</v>
+      </c>
+      <c r="K26" s="0">
+        <v>13076</v>
+      </c>
+      <c r="L26" s="0">
+        <v>1097</v>
+      </c>
+      <c r="M26" s="0">
+        <v>2166</v>
+      </c>
+      <c r="N26" s="0">
+        <v>592</v>
+      </c>
+      <c r="O26" s="0">
+        <v>10060</v>
+      </c>
+      <c r="P26" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="0">
+        <v>109470</v>
+      </c>
+      <c r="R26" s="0">
+        <v>109470</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>1766</v>
+      </c>
+      <c r="C27" s="0">
+        <v>6766</v>
+      </c>
+      <c r="D27" s="0">
+        <v>60</v>
+      </c>
+      <c r="E27" s="0">
+        <v>11492</v>
+      </c>
+      <c r="F27" s="0">
+        <v>1941</v>
+      </c>
+      <c r="G27" s="0">
+        <v>389</v>
+      </c>
+      <c r="H27" s="0">
+        <v>364</v>
+      </c>
+      <c r="I27" s="0">
+        <v>240</v>
+      </c>
+      <c r="J27" s="0">
+        <v>480</v>
+      </c>
+      <c r="K27" s="0">
+        <v>13</v>
+      </c>
+      <c r="L27" s="0">
+        <v>177</v>
+      </c>
+      <c r="M27" s="0">
+        <v>439</v>
+      </c>
+      <c r="N27" s="0">
+        <v>199</v>
+      </c>
+      <c r="O27" s="0">
+        <v>736</v>
+      </c>
+      <c r="P27" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="0">
+        <v>25062</v>
+      </c>
+      <c r="R27" s="0">
+        <v>25062</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>1805</v>
+      </c>
+      <c r="C28" s="0">
+        <v>14848</v>
+      </c>
+      <c r="D28" s="0">
+        <v>1724</v>
+      </c>
+      <c r="E28" s="0">
+        <v>10210</v>
+      </c>
+      <c r="F28" s="0">
+        <v>7403</v>
+      </c>
+      <c r="G28" s="0">
+        <v>44</v>
+      </c>
+      <c r="H28" s="0">
+        <v>3854</v>
+      </c>
+      <c r="I28" s="0">
+        <v>2306</v>
+      </c>
+      <c r="J28" s="0">
+        <v>5361</v>
+      </c>
+      <c r="K28" s="0">
+        <v>0</v>
+      </c>
+      <c r="L28" s="0">
+        <v>1213</v>
+      </c>
+      <c r="M28" s="0">
+        <v>909</v>
+      </c>
+      <c r="N28" s="0">
+        <v>0</v>
+      </c>
+      <c r="O28" s="0">
+        <v>2004</v>
+      </c>
+      <c r="P28" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="0">
+        <v>51681</v>
+      </c>
+      <c r="R28" s="0">
+        <v>51681</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>6887</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>77560</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>1951</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>116020</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>45351</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G29" s="0">
         <v>440</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H29" s="0">
         <v>25013</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I29" s="0">
         <v>6410</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J29" s="0">
         <v>84906</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K29" s="0">
         <v>32646</v>
       </c>
-      <c r="L25" s="0">
+      <c r="L29" s="0">
         <v>6217</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M29" s="0">
         <v>18785</v>
       </c>
-      <c r="N25" s="0">
+      <c r="N29" s="0">
         <v>4591</v>
       </c>
-      <c r="O25" s="0">
+      <c r="O29" s="0">
         <v>28661</v>
       </c>
-      <c r="P25" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="0">
+      <c r="P29" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="0">
         <v>455438</v>
       </c>
-      <c r="R25" s="0">
+      <c r="R29" s="0">
         <v>455438</v>
       </c>
     </row>
